--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,37 +27,15 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -86,22 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,1932 +435,1978 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A3:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16.5" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="3.14" customWidth="1" min="1" max="1"/>
+    <col width="34.43" customWidth="1" min="2" max="2"/>
+    <col width="17.29" customWidth="1" min="3" max="3"/>
+    <col width="13.43" customWidth="1" min="4" max="4"/>
+    <col width="17.86" customWidth="1" min="5" max="5"/>
+    <col width="22.57" customWidth="1" min="6" max="6"/>
+    <col width="21.71" customWidth="1" min="7" max="7"/>
+    <col width="17.71" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="26.29" customWidth="1" min="10" max="10"/>
+    <col width="13.86" customWidth="1" min="11" max="11"/>
+    <col width="16.43" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh 26-02 (30 nafar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Namuna: Saydalimov Anvarjon Sarvarjon o`g`li | 517******0016 | AC1686958 | 990201527 | Qashqadaryo, Qarshi | 4-mittituman 21/23 | Qarshi shahar 1-maktab | Qarshi City School No. 1 | Школа №1 города Карши | Maktab | AA1775603 | 2008-2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Avval o`qigan muassasa nomi(Rus tilida)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Alimova Sevinch Raxmiddin qizi</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>62707005740020</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>AB7974700</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="2" t="n">
         <v>700343131</v>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qarshi tumani</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Qarshi Pedagogical College</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Каршинский педагогический колледж</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>K 5486730</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Berdiqulova Gulshan Rustam qizi</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>41001955590049</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>AE6702868</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>770629890</v>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz texnologiya kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Technology</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский технологический профессиональный колледж</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>K 0162430</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2010-2013</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Eshmurotova Charos Bekqul qizi</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>61901085720047</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AE5720760</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>886177860</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="2" t="n">
         <v>914577860</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №6 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>UM 03717179</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>61206085590028</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>AD8701218</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>880052965</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="2" t="n">
         <v>874861208</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №7 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>UM 03751895</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Hamroqulova Farzona Odilovna</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>62111085680033</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>AE4371486</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="2" t="n">
         <v>870102621</v>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 52-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 52, Kitob District</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №52 Китабского района</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>UM 03729539</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Hasanova Dilnura Eson qizi</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>61508085680038</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>AE3555106</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>875681508</v>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 24-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 24, Kitob District</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №24 Китабского района</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>UM 03728724</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Hasanova Marjona Xolmurod qizi</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>60411085680047</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>AE5685784</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="2" t="n">
         <v>973350582</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="2" t="n">
         <v>978635082</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 47-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 47, Kitob District</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №47 Китабского района</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>UM 03729364</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Ilhomova Zuhra Davron qizi</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>63110085590015</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AE4378923</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>881151031</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>881840585</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>UM 03752606</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Islomova Nilufar Abdulxafiz qizi</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>61911085590104</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>AD9664280</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="2" t="n">
         <v>912174355</v>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №14 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>UM 03752502</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>62207085680059</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>AE3492384</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>918112208</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="2" t="n">
         <v>918151309</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 47-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 47, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №47 Китабского района</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>UM 03729365</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>62401095680012</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>AE5222372</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="2" t="n">
         <v>880880124</v>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №45 Китабского района</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>UM 03729316</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>60201085630050</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AE5088010</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Чиракчинского района</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>UM 03742126</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>61202005680055</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>AB7137876</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Китабский профессиональный колледж агробизнеса</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>K 5470992</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>62410085590084</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>AE1067914</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>975855793</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="2" t="n">
         <v>776070824</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>UM 03752610</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Nurillayeva Dilsuz Mashrabovna</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>42506912640010</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>AD4774693</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Kitob iqtisodiyot kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Kitob Vocational College of Economics</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>K 1607691</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2007-2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>62012085590055</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>AE4084333</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>992460829</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F19" s="2" t="n">
         <v>701080829</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 34-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 34, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №34 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>UM 03754418</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Qulmatova Shabbona Azamat qizi</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>61008085680019</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>AE4905104</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>778338272</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>General Secondary School No. 70, Kitob District</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>UM 03730102</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2015-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>60406055720067</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>AE7231113</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>908785105</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F21" s="2" t="n">
         <v>916397685</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Specialized School, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Специализированная школа города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>UM 02138929</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>61608085630072</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>AE5324961</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Чиракчинского района</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>UM 03742132</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>40710895590044</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>AE1836076</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>976312909</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F23" s="2" t="n">
         <v>953332960</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №26 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>O'R-SH 0658073</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>1996-2007</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>42910905720012</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>AD8980430</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>912192099</v>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani 1-sonli ixtisoslashtirilgan maktab-internati</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Specialized Boarding School No. 1, Chiroqchi District</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>OR-SH 0346677</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1997-2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>61807085590034</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>AE3352294</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>770578758</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F25" s="2" t="n">
         <v>704897375</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №29 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>UM 03754198</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>61311085680032</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>AE4233482</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Kitob tumani 78-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>General Secondary School No. 78, Kitob District</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2015-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>62103085590038</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>AD7767171</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>200132207</v>
       </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №6 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>UM 03751877</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>61409005680027</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>AB7166586</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E28" s="2" t="n">
         <v>996152272</v>
       </c>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness and Services</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Китабский профессиональный колледж агробизнеса и сервиса</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>K 5491697</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>62709085590070</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>AE3558477</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>885890027</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F29" s="2" t="n">
         <v>957701169</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №29 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>UM 03754217</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>61906085680012</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>AE5199773</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E30" s="2" t="n">
         <v>880115819</v>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 11, Kitob District</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №11 Китабского района</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>UM 03728346</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>40404975650046</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>AD4186169</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>916499228</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F31" s="2" t="n">
         <v>976015200</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qarshi tumani</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Qarshi College of Economics</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Каршинский экономический колледж</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>K 3736287</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2012-2015</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>51106085680031</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AE4503488</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Китабского района</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>UM 03730110</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>60512085590078</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>AE5293914</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>880669272</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F33" s="2" t="n">
         <v>952556670</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №29 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>UM 03754201</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>60402095590060</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>AE4989343</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E34" s="2" t="n">
         <v>334948423</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F34" s="2" t="n">
         <v>991840519</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 19, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №19 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>UM 03752857</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>41406985680067</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>AE7821304</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>700720614</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F35" s="2" t="n">
         <v>992558990</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agro-Services</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Китабский профессиональный колледж агросервиса</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>K 4590366</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>2014-2017</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>62704025590042</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>AC1967100</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>880088028</v>
       </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №29 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>UM 0438281</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>2009-2020</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>42207935680042</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>AB9239333</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E37" s="2" t="n">
         <v>771219093</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F37" s="2" t="n">
         <v>889770693</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Kitob District</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №45 Китабского района</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>UM 03524597</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2025 (eksternat)</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
@@ -435,22 +435,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M37"/>
+  <dimension ref="A3:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.14" customWidth="1" min="1" max="1"/>
-    <col width="34.43" customWidth="1" min="2" max="2"/>
-    <col width="17.29" customWidth="1" min="3" max="3"/>
-    <col width="13.43" customWidth="1" min="4" max="4"/>
-    <col width="17.86" customWidth="1" min="5" max="5"/>
-    <col width="22.57" customWidth="1" min="6" max="6"/>
-    <col width="21.71" customWidth="1" min="7" max="7"/>
-    <col width="17.71" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26.29" customWidth="1" min="10" max="10"/>
-    <col width="13.86" customWidth="1" min="11" max="11"/>
-    <col width="16.43" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34.43" customWidth="1" min="3" max="3"/>
+    <col width="17.29" customWidth="1" min="4" max="4"/>
+    <col width="13.43" customWidth="1" min="5" max="5"/>
+    <col width="17.86" customWidth="1" min="6" max="6"/>
+    <col width="22.57" customWidth="1" min="7" max="7"/>
+    <col width="21.71" customWidth="1" min="8" max="8"/>
+    <col width="17.71" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="26.29" customWidth="1" min="11" max="11"/>
+    <col width="13.86" customWidth="1" min="12" max="12"/>
+    <col width="16.43" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="3" ht="47.25" customHeight="1">
@@ -461,60 +462,65 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>Guruhi</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
@@ -526,50 +532,55 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>Alimova Sevinch Raxmiddin qizi</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>62707005740020</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AB7974700</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>700343131</v>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qarshi tumani</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Qarshi Pedagogical College</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>K 5486730</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -581,50 +592,55 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Berdiqulova Gulshan Rustam qizi</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>41001955590049</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>AE6702868</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>770629890</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz texnologiya kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Technology</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>K 0162430</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2010-2013</t>
         </is>
@@ -636,52 +652,57 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Eshmurotova Charos Bekqul qizi</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>61901085720047</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AE5720760</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>886177860</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>914577860</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>UM 03717179</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -693,52 +714,57 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>G'aybullayeva Ruxsora Xusniddin qizi</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>61206085590028</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>AD8701218</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>880052965</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>874861208</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>UM 03751895</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -750,50 +776,55 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>Hamroqulova Farzona Odilovna</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>62111085680033</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AE4371486</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>870102621</v>
       </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 52-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 52, Kitob District</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>UM 03729539</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -805,50 +836,55 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Hasanova Dilnura Eson qizi</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>61508085680038</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AE3555106</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>875681508</v>
       </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 24-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 24, Kitob District</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>UM 03728724</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -860,52 +896,57 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Hasanova Marjona Xolmurod qizi</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>60411085680047</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AE5685784</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>973350582</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>978635082</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 47-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 47, Kitob District</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>UM 03729364</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -917,52 +958,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Ilhomova Zuhra Davron qizi</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>63110085590015</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>AE4378923</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>881151031</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>881840585</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>UM 03752606</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -974,50 +1020,55 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Islomova Nilufar Abdulxafiz qizi</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>61911085590104</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AD9664280</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>912174355</v>
       </c>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>UM 03752502</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1029,52 +1080,57 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Jalolova Rayxona Akmal qizi</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>62207085680059</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>AE3492384</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>918112208</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>918151309</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 47-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 47, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>UM 03729365</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1086,50 +1142,55 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>62401095680012</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>AE5222372</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>880880124</v>
       </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>UM 03729316</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1141,48 +1202,53 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>Maxmashoxova Feruza Bekmurod qizi</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>60201085630050</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AE5088010</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t>UM 03742126</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1194,48 +1260,53 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Meyliqulova Hilola Farhod qizi</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>61202005680055</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AB7137876</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>K 5470992</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1247,52 +1318,57 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>Nu'monova Saidabonu Ulug'bek qizi</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>62410085590084</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AE1067914</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>975855793</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>776070824</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>UM 03752610</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1304,48 +1380,53 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Nurillayeva Dilsuz Mashrabovna</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>42506912640010</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AD4774693</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Kitob iqtisodiyot kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Economics</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>K 1607691</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2007-2010</t>
         </is>
@@ -1357,52 +1438,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>Ochildiyeva Dinora Otabek qizi</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>62012085590055</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>AE4084333</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>992460829</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>701080829</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 34-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 34, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>UM 03754418</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1414,50 +1500,55 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>61008085680019</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>AE4905104</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>778338272</v>
       </c>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>UM 03730102</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1469,52 +1560,57 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Quysinova Rohshona To'lqin qizi</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>60406055720067</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>AE7231113</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>908785105</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>916397685</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Specialized School, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>UM 02138929</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -1526,48 +1622,53 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>61608085630072</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AE5324961</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>UM 03742132</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1579,52 +1680,57 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>Samadova Nigora Abdisamiyevna</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>40710895590044</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AE1836076</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>976312909</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>953332960</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>O'R-SH 0658073</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>1996-2007</t>
         </is>
@@ -1636,50 +1742,55 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Samatova Oydin Sulaymon qizi</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>42910905720012</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AD8980430</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>912192099</v>
       </c>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 1-sonli ixtisoslashtirilgan maktab-internati</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Specialized Boarding School No. 1, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>OR-SH 0346677</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>1997-2008</t>
         </is>
@@ -1691,52 +1802,57 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>Saydalimova Ruxshona Sharofiddin qizi</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>61807085590034</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>AE3352294</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>770578758</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>704897375</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>UM 03754198</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1748,48 +1864,53 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>Shonazarova Vazira Botir qizi</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>61311085680032</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AE4233482</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 78-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 78, Kitob District</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>UM 03730412</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1801,50 +1922,55 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>Shukriyeva Nariye Redvanovna</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>62103085590038</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>AD7767171</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>200132207</v>
       </c>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t>UM 03751877</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1856,50 +1982,55 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Suyunova Maftuna Akbar qizi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>61409005680027</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AB7166586</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>996152272</v>
       </c>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness and Services</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>K 5491697</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1911,52 +2042,57 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>To'raboyeva Sabrina Ovlaqul qizi</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>62709085590070</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>AE3558477</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>885890027</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>957701169</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>UM 03754217</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1968,50 +2104,55 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>61906085680012</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>AE5199773</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>880115819</v>
       </c>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 11, Kitob District</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>UM 03728346</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2023,52 +2164,57 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>Tosheva Aziza Sherzod qizi</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>40404975650046</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>AD4186169</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>916499228</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>976015200</v>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qarshi tumani</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Qarshi iqtisodiyot kolleji</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Qarshi College of Economics</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>K 3736287</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>2012-2015</t>
         </is>
@@ -2080,50 +2226,55 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>Tursunov Sohibjon Hakim o'g'li</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>51106085680031</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>AE4503488</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>UM 03730110</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2135,52 +2286,57 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Umarova Iroda Muzaffar qizi</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>60512085590078</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>AE5293914</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>880669272</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>952556670</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>UM 03754201</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2192,52 +2348,57 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Uroqova Jasmina Jasur qizi</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>60402095590060</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>AE4989343</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>334948423</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>991840519</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 19-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 19, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>UM 03752857</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2249,52 +2410,57 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>Usmanova Iroda Abdurazzoq qizi</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>41406985680067</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>AE7821304</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>700720614</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>992558990</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agro-Services</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>K 4590366</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>2014-2017</t>
         </is>
@@ -2306,50 +2472,55 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>Xurramova Shodiya Arol qizi</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>62704025590042</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>AC1967100</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>880088028</v>
       </c>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>UM 0438281</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>2009-2020</t>
         </is>
@@ -2361,52 +2532,57 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>Yorboboyeva Mahliyo Xusan qizi</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>42207935680042</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>AB9239333</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>771219093</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>889770693</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Kitob District</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t>UM 03524597</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>2025 (eksternat)</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
@@ -551,15 +551,21 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>700343131</v>
-      </c>
-      <c r="G4" s="2" t="n"/>
+        <v>3431310</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>3431310</v>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Qarshi tumani</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Guluston, Guluston, 4.0</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Qarshi pedagogika kolleji</t>
@@ -611,15 +617,21 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>770629890</v>
-      </c>
-      <c r="G5" s="2" t="n"/>
+        <v>706298900</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>973196260</v>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Kesh MFY, Kalakon kucha, 91-uy</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz texnologiya kasb-hunar kolleji</t>
@@ -671,17 +683,19 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>886177860</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>914577860</v>
-      </c>
+        <v>976190215</v>
+      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Pakkandi MFY, Safarabot, 29_uy</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 6-sonli umumiy o'rta ta'lim maktabi</t>
@@ -740,10 +754,14 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Kesh MFY, Kesh ko'chasi, 102-uy</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
@@ -795,15 +813,21 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>870102621</v>
-      </c>
-      <c r="G8" s="2" t="n"/>
+        <v>701026210</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>977011783</v>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Qurilish, Varganza shaharchasi, 220-uy</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 52-sonli umumiy o'rta ta'lim maktabi</t>
@@ -855,15 +879,21 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>875681508</v>
-      </c>
-      <c r="G9" s="2" t="n"/>
+        <v>756815080</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>885857068</v>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Yangizamon, Durmon koʻchasi, 136-uy</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 24-sonli umumiy o'rta ta'lim maktabi</t>
@@ -977,17 +1007,21 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>881151031</v>
+        <v>811510310</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>881840585</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Zargarlik MFY, Yakdillik ko'chasi, 186-uy</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1161,15 +1195,21 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>880880124</v>
-      </c>
-      <c r="G14" s="2" t="n"/>
+        <v>808801240</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>156130020</v>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Sevaz MFY, Taraqqiyot kuchasi, 130-uy</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1220,14 +1260,22 @@
           <t>AE5088010</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="F15" s="2" t="n">
+        <v>184403080</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>195942150</v>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t>Qashqadaryo, Qiziltepa tumani</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Yuksalish mfy, Roxat koʻchasi, 44.0</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1278,14 +1326,22 @@
           <t>AB7137876</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
+      <c r="F16" s="2" t="n">
+        <v>721302400</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>861885800</v>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Palandara MFY, Oftobroʻya qishlogʻi, 35.0</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
@@ -1337,17 +1393,21 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>975855793</v>
+        <v>776070824</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>776070824</v>
+        <v>739901790</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Ipak Yuli, Ipak Yuli, 118/26</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1457,17 +1517,21 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
+        <v>701080829</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>992460829</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>701080829</v>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Abziyat MFY, Bahor kuchasi, 62_-uy</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 34-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1579,17 +1643,21 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>908785105</v>
+        <v>87851050</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>916397685</v>
+        <v>163976850</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Taraģay, Chuyut, 153-uy</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri ixtisoslashtirilgan maktabi</t>
@@ -1640,14 +1708,22 @@
           <t>AE5324961</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="F22" s="2" t="n">
+        <v>505054080</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>906262080</v>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n"/>
+          <t>Qashqadaryo, Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Yuksalish MFY, Olmazor, 183.0</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1699,17 +1775,21 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>976312909</v>
+        <v>163545560</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>953332960</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Turon, Zarafshon, 12.01</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1821,17 +1901,21 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
+        <v>704897375</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>770578758</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>704897375</v>
-      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Shanbe MFY, Chorvodor koʻcha, 10 uy</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1941,15 +2025,21 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>200132207</v>
-      </c>
-      <c r="G27" s="2" t="n"/>
+        <v>770850627</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>880850627</v>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Ipak yo’li, Ipak yo’li, 118/28</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2001,15 +2091,21 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>996152272</v>
-      </c>
-      <c r="G28" s="2" t="n"/>
+        <v>794119200</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>961522720</v>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Zarafshon MFY, Yangiobod shaharchasi, 432.0</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani agrobiznes va xizmat ko'rsatish kasb-hunar kolleji</t>
@@ -2061,17 +2157,21 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>885890027</v>
+        <v>886899080</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>957701169</v>
+        <v>577011690</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Shanbe MFY, Shabboda, 35 -uy</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2123,15 +2223,21 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>880115819</v>
-      </c>
-      <c r="G30" s="2" t="n"/>
+        <v>801158190</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>505870874</v>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Boģbon MFY, Ochamayli kòchasi, 100-uy</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2183,17 +2289,21 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>916499228</v>
+        <v>146492280</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>976015200</v>
+        <v>886015200</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Qarshi tumani</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Kesh MFY, Do'stlik ko'chasi, 31/9-dom</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Qarshi iqtisodiyot kolleji</t>
@@ -2245,15 +2355,21 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>995658681</v>
-      </c>
-      <c r="G32" s="2" t="n"/>
+        <v>593907050</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>991437903</v>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Navbaxor MFY, Bolton qaychili, 99-uy</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2305,17 +2421,21 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>880669272</v>
+        <v>736908720</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>952556670</v>
+        <v>806692720</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Shanbe MFY, Chorvador ko'chasi, 36-uy</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2370,14 +2490,18 @@
         <v>334948423</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>991840519</v>
+        <v>494842333</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>G'arov, G'arov kuchasi, 84.0</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 19-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2429,17 +2553,21 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>700720614</v>
+        <v>7206140</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>992558990</v>
+        <v>577415640</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Jilisuv QFY, Chimboy, 19 uy</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Kitob agroservis xizmat ko'rsatish kasb-hunar kolleji</t>
@@ -2491,15 +2619,21 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>880088028</v>
-      </c>
-      <c r="G36" s="2" t="n"/>
+        <v>700880280</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>880280880</v>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n"/>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Bo'ston mahallaa, Shodlik kuchasi, 140 uy</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 29-sonli umumiy o'rta ta'lim maktabi</t>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-02).xlsx
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3431310</v>
+        <v>700343131</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3431310</v>
+        <v>700343131</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Guluston, Guluston, 4.0</t>
+          <t>Guluston, Guluston, 4-uy</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -617,14 +617,14 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>706298900</v>
+        <v>770629890</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>973196260</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -685,7 +685,9 @@
       <c r="F6" s="2" t="n">
         <v>976190215</v>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="n">
+        <v>887311969</v>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
@@ -754,7 +756,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, shahrizabz shahar</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -813,14 +815,14 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>701026210</v>
+        <v>870102621</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>977011783</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
+          <t>Qashqadaryo viloyati Kitob tumani</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -879,7 +881,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>756815080</v>
+        <v>875681508</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>885857068</v>
@@ -945,17 +947,21 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>973350582</v>
+        <v>978635082</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>978635082</v>
+        <v>973550582</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Saroy MFY, Yangiqishloq, 44-uy</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 47-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1007,14 +1013,14 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>811510310</v>
+        <v>881151031</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>881840585</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1073,15 +1079,21 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
+        <v>778641917</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>912174355</v>
       </c>
-      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Turon MFY, Yangi obod, 62-uy</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1136,14 +1148,18 @@
         <v>918112208</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>918151309</v>
+        <v>918172073</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Saroy MFY, Saroy koʻchasi, 17-uy</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 47-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1195,14 +1211,14 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>808801240</v>
+        <v>880880124</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>156130020</v>
+        <v>915613002</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
+          <t>Qashqadaryo, Kotob tumani</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1261,19 +1277,19 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>184403080</v>
+        <v>918440308</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>195942150</v>
+        <v>919594215</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Qiziltepa tumani</t>
+          <t>Qashqadaryo, Qizil tepa</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Yuksalish mfy, Roxat koʻchasi, 44.0</t>
+          <t>Yuksalish mfy, Roxat koʻchasi, 44-uy</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1327,10 +1343,10 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>721302400</v>
+        <v>872130240</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>861885800</v>
+        <v>886188580</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1339,7 +1355,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Palandara MFY, Oftobroʻya qishlogʻi, 35.0</t>
+          <t>Palandara MFY, Oftobroʻya qishlogʻi, 35-uy</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1396,11 +1412,11 @@
         <v>776070824</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>739901790</v>
+        <v>873990179</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1524,7 +1540,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1643,10 +1659,10 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>87851050</v>
+        <v>908785105</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>163976850</v>
+        <v>916397685</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1709,19 +1725,19 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>505054080</v>
+        <v>950505408</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>906262080</v>
+        <v>990626208</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Qamashi tumani</t>
+          <t>Qashqadaryo, Qamashi</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Yuksalish MFY, Olmazor, 183.0</t>
+          <t>Yuksalish MFY, Olmazor, 183-uy</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1775,14 +1791,14 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>163545560</v>
+        <v>916354556</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>953332960</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1908,7 +1924,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shaxrisabz tumani</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1966,14 +1982,22 @@
           <t>AE4233482</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="F26" s="2" t="n">
+        <v>500026078</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>500026078</v>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo MFY, Minjir qishlogʻi, 51-uy</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 78-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2032,7 +2056,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2091,10 +2115,10 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>794119200</v>
+        <v>879411920</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>961522720</v>
+        <v>996152272</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2103,7 +2127,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Zarafshon MFY, Yangiobod shaharchasi, 432.0</t>
+          <t>Zarafshon MFY, Yangiobod shaharchasi, 432-uy</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2157,19 +2181,19 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>886899080</v>
+        <v>883367774</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>577011690</v>
+        <v>907163142</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Shanbe MFY, Shabboda, 35 -uy</t>
+          <t>Do'stlik MFY, Bunyodkor ko'chasi, 62/16-uy</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2223,10 +2247,10 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>801158190</v>
+        <v>880115819</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>505870874</v>
+        <v>874650587</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2289,14 +2313,14 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>146492280</v>
+        <v>914649228</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>886015200</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shaxrsabz shahar</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2355,7 +2379,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>593907050</v>
+        <v>959390705</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>991437903</v>
@@ -2421,14 +2445,14 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>736908720</v>
+        <v>873690872</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>806692720</v>
+        <v>880669272</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2490,16 +2514,16 @@
         <v>334948423</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>494842333</v>
+        <v>334948423</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>G'arov, G'arov kuchasi, 84.0</t>
+          <t>G'arov, G'arov kuchasi, 84-uy</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2553,10 +2577,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>7206140</v>
+        <v>700720614</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>577415640</v>
+        <v>957741564</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2643,10 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>700880280</v>
+        <v>970088028</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>880280880</v>
+        <v>880088028</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2688,14 +2712,18 @@
         <v>771219093</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>889770693</v>
+        <v>992019274</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Ayoqchi MFY, Qovchin qishlogʻi, 92uy</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
